--- a/risorse/Risorsa_11_Chiusura_Mensile.xlsx
+++ b/risorse/Risorsa_11_Chiusura_Mensile.xlsx
@@ -17,10 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00;-"/>
-  </numFmts>
-  <fonts count="7">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,38 +27,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <color rgb="001E3A5F"/>
+      <sz val="15"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="0000838F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001E3A5F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,26 +60,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000BCD4"/>
+        <fgColor rgb="001E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A1F2E"/>
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000838F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C62828"/>
+        <fgColor rgb="00F5A623"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -96,107 +82,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CFD8DC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CFD8DC"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CFD8DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFCDD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C8E6C9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -558,33 +461,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · Risorsa 11 — Chiusura Mensile</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — Risorsa 11 · Chiusura Mensile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Categorizzazione spese e P&amp;L semplificato</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>Inserisci i movimenti: il P&amp;L si calcola da solo. Le uscite vanno con il segno meno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Data</t>
@@ -622,32 +525,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Fattura cliente Rossi SRL</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ricavi</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Servizi consulenza</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -677,38 +580,39 @@
           <t>Uscita</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="4" t="n">
         <v>-2200</v>
       </c>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Abbonamento ChatGPT Plus</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Software/AI</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>AI tools</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>-22</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-20</v>
       </c>
     </row>
     <row r="8">
@@ -737,37 +641,38 @@
           <t>Uscita</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>-800</v>
       </c>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Bolletta luce</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Utenze</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>-180</v>
       </c>
     </row>
@@ -797,37 +702,38 @@
           <t>Entrata</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="4" t="n">
         <v>6200</v>
       </c>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Materiale ufficio</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Costi operativi</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Cancelleria</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>-120</v>
       </c>
     </row>
@@ -857,37 +763,38 @@
           <t>Uscita</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="4" t="n">
         <v>-350</v>
       </c>
+      <c r="G12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Commercialista</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Servizi professionali</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Consulenza fiscale</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -917,473 +824,120 @@
           <t>Entrata</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="4" t="n">
         <v>3800</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="4" t="n"/>
-    </row>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="4" t="n"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="4" t="n"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="4" t="n"/>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="4" t="n"/>
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="4" t="n"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="4" t="n"/>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="4" t="n"/>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="4" t="n"/>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="4" t="n"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="4" t="n"/>
       <c r="B30" s="4" t="n"/>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
-      <c r="F30" s="5" t="n"/>
+      <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="4" t="n"/>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="n"/>
       <c r="B32" s="4" t="n"/>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="4" t="n"/>
       <c r="B34" s="4" t="n"/>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
-      <c r="F34" s="5" t="n"/>
+      <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n"/>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n"/>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="4" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n"/>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n"/>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n"/>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n"/>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n"/>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n"/>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n"/>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="4" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="n"/>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="n"/>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n"/>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n"/>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n"/>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="4" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="n"/>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n"/>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="4" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="F5:F64">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Ricavi,Costi personale,Costi fissi,Software/AI,Utenze,Costi operativi,Marketing,Servizi professionali"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Entrata,Uscita"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1394,25 +948,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · P&amp;L Mensile</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — P&amp;L Mensile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aggregato per categoria — formule live</t>
+          <t>Aggregato per categoria, con formule live dai Movimenti.</t>
         </is>
       </c>
     </row>
@@ -1434,177 +988,167 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Ricavi</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
       </c>
-      <c r="C5" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A5,Movimenti!F5:F64)</f>
+      <c r="C5">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A5,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Costi personale</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="C6" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A6,Movimenti!F5:F64)</f>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A6,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Costi fissi</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="C7" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A7,Movimenti!F5:F64)</f>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A7,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Software/AI</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="C8" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A8,Movimenti!F5:F64)</f>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A8,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Utenze</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="C9" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A9,Movimenti!F5:F64)</f>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A9,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Costi operativi</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="C10" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A10,Movimenti!F5:F64)</f>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A10,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="C11" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A11,Movimenti!F5:F64)</f>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A11,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Servizi professionali</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Uscita</t>
-        </is>
-      </c>
-      <c r="C12" s="5">
-        <f>SUMIF(Movimenti!C5:C64,A12,Movimenti!F5:F64)</f>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Uscita</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>SUMIF(Movimenti!$C$5:$C$34,A12,Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TOTALE ENTRATE</t>
+        </is>
+      </c>
+      <c r="C13" s="5">
+        <f>SUMIF(Movimenti!$E$5:$E$34,"Entrata",Movimenti!$F$5:$F$34)</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>TOTALE ENTRATE</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8">
-        <f>SUMIF(B5:B12,"Entrata",C5:C12)</f>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TOTALE USCITE</t>
+        </is>
+      </c>
+      <c r="C14" s="5">
+        <f>SUMIF(Movimenti!$E$5:$E$34,"Uscita",Movimenti!$F$5:$F$34)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>TOTALE USCITE</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="8">
-        <f>SUMIF(B5:B12,"Uscita",C5:C12)</f>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>MARGINE</t>
+        </is>
+      </c>
+      <c r="C15" s="6">
+        <f>C13+C14</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>MARGINE</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="10">
-        <f>C14+C15</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>